--- a/data/themes/countries/countries.xlsx
+++ b/data/themes/countries/countries.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Албанский лек</t>
+          <t>Лек</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ангольская кванза</t>
+          <t>Кванза</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Армянский драм</t>
+          <t>Драм</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Афганский афгани</t>
+          <t>Афгани</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Бангладешская така</t>
+          <t>Така</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Болгарский лев</t>
+          <t>Лев</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Конвертируемая марка</t>
+          <t>Марка</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ботсванская пула</t>
+          <t>Пула</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Бразильский реал</t>
+          <t>Реал</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Венгерский форинт</t>
+          <t>Форинт</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Вьетнамский донг</t>
+          <t>Донг</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Гаитянский гурд</t>
+          <t>Гурд</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ганский седи</t>
+          <t>Седи</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Грузинский лари</t>
+          <t>Лари</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Новый израильский шекель</t>
+          <t>Шекель</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Казахстанский тенге</t>
+          <t>Тенге</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Камбоджийский риель</t>
+          <t>Риель</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Киргизский сом</t>
+          <t>Сом</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Коста-риканский колон</t>
+          <t>Колон</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Лаосский кип</t>
+          <t>Кип</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Малагасийский ариари</t>
+          <t>Ариари</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Малайзийский ринггит</t>
+          <t>Ринггит</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Мальдивская руфия</t>
+          <t>Руфия</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Мозамбикский метикал</t>
+          <t>Метикал</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Монгольский тугрик</t>
+          <t>Тугрик</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Мьянманский кьят</t>
+          <t>Кьят</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Папуа-ново-гвинейская кина</t>
+          <t>Кина</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Перуанский соль</t>
+          <t>Соль</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Македонский денар</t>
+          <t>Денар</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Тайский бат</t>
+          <t>Бат</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Турецкая лира</t>
+          <t>Лира</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Узбекский сум</t>
+          <t>Сум</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Эфиопский быр</t>
+          <t>Быр</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Южноафриканский рэнд</t>
+          <t>Рэнд</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Японская иена</t>
+          <t>Иена</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
